--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486364_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486364_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0877</v>
+        <v>3.6871</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7036</v>
+        <v>1.8406</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3841</v>
+        <v>1.8465</v>
       </c>
       <c r="G2" t="n">
         <v>1.4828</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0823</v>
+        <v>0.6817</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4879</v>
+        <v>-0.3509</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5702</v>
+        <v>1.0325</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DOMENECH FONTANA</t>
+          <t>A. GARUBA ALARI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2737</v>
+        <v>2.3934</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8344</v>
+        <v>0.6849</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4393</v>
+        <v>1.7085</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7511</v>
+        <v>2.3732</v>
       </c>
       <c r="H3" t="n">
-        <v>2.3934</v>
+        <v>0.958</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6423</v>
+        <v>1.4152</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1068</v>
+        <v>1.9286</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5586</v>
+        <v>0.876</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.4519</v>
+        <v>1.0527</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3556</v>
+        <v>0.4446</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1652</v>
+        <v>0.082</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8096</v>
+        <v>0.3626</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1751</v>
+        <v>-1.305</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7401</v>
+        <v>0.2376</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3377</v>
+        <v>0.0613</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4024</v>
+        <v>0.1763</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8624</v>
+        <v>1.5526</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.2474</v>
+        <v>-1.6633</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1098</v>
+        <v>3.2159</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4688</v>
@@ -766,13 +766,13 @@
         <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3785</v>
+        <v>1.0686</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3699</v>
+        <v>-0.7859</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7484</v>
+        <v>1.8545</v>
       </c>
       <c r="V4" t="n">
         <v>3.7804</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GARUBA ALARI</t>
+          <t>A. DOMENECH FONTANA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8355</v>
+        <v>1.1831</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2811</v>
+        <v>0.0521</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5544</v>
+        <v>1.1311</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3732</v>
+        <v>1.7511</v>
       </c>
       <c r="H5" t="n">
-        <v>0.958</v>
+        <v>2.3934</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4152</v>
+        <v>-0.6423</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9286</v>
+        <v>2.1068</v>
       </c>
       <c r="K5" t="n">
-        <v>0.876</v>
+        <v>3.5586</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0527</v>
+        <v>-1.4519</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4446</v>
+        <v>-0.3556</v>
       </c>
       <c r="N5" t="n">
-        <v>0.082</v>
+        <v>-1.1652</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3626</v>
+        <v>0.8096</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3203</v>
+        <v>0.6495</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3425</v>
+        <v>-0.4446</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0222</v>
+        <v>1.0941</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6379</v>
+        <v>0.4944</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1294</v>
+        <v>-0.3962</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7673</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3504</v>
@@ -922,13 +922,13 @@
         <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3358</v>
+        <v>0.1923</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3341</v>
+        <v>0.0673</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0017</v>
+        <v>0.125</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.049</v>
+        <v>0.0435</v>
       </c>
       <c r="E7" t="n">
         <v>-0.5493</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5003</v>
+        <v>0.5928</v>
       </c>
       <c r="G7" t="n">
         <v>-0.8622</v>
@@ -1000,13 +1000,13 @@
         <v>0.6525</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5789</v>
+        <v>-0.4864</v>
       </c>
       <c r="T7" t="n">
         <v>-0.536</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0429</v>
+        <v>0.0496</v>
       </c>
       <c r="V7" t="n">
         <v>0.7395</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>A. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9076</v>
+        <v>-0.9443</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9742</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0665</v>
+        <v>-0.223</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0226</v>
+        <v>-1.6915</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4896</v>
+        <v>-0.3225</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.467</v>
+        <v>-1.369</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0793</v>
+        <v>-0.5591</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8244</v>
+        <v>0.1095</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7451</v>
+        <v>-0.6686</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0567</v>
+        <v>-1.1324</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3348</v>
+        <v>-0.432</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2781</v>
+        <v>-0.7004</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2225</v>
+        <v>0.0946</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8784</v>
+        <v>-0.1622</v>
       </c>
       <c r="U8" t="n">
-        <v>1.101</v>
+        <v>0.2569</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. MARTIN MARIN</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0439</v>
+        <v>-1.0425</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.4624</v>
+        <v>-2.8624</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4185</v>
+        <v>1.8199</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2978</v>
+        <v>0.0226</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3193</v>
+        <v>0.4896</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9785</v>
+        <v>-0.467</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.305</v>
+        <v>0.0793</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8149</v>
+        <v>0.8244</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4901</v>
+        <v>-0.7451</v>
       </c>
       <c r="M9" t="n">
-        <v>1.0072</v>
+        <v>-0.0567</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4956</v>
+        <v>-0.3348</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.2781</v>
       </c>
       <c r="P9" t="n">
-        <v>1.0875</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2963</v>
+        <v>0.0877</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0601</v>
+        <v>-0.7667</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2362</v>
+        <v>0.8544</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.13</v>
+        <v>0.3698</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. HARGUINDEY MANEIRO</t>
+          <t>A. MARTIN MARIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2787</v>
+        <v>-1.1258</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9015</v>
+        <v>-2.7292</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3771</v>
+        <v>1.6034</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.6915</v>
+        <v>-1.2978</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3225</v>
+        <v>-0.3193</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.369</v>
+        <v>-0.9785</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5591</v>
+        <v>-2.305</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1095</v>
+        <v>-0.8149</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6686</v>
+        <v>-1.4901</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1324</v>
+        <v>1.0072</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.432</v>
+        <v>0.4956</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7004</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2397</v>
+        <v>0.2145</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3425</v>
+        <v>-0.2067</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1027</v>
+        <v>0.4212</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.2048</v>
+        <v>-5.7689</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2483</v>
+        <v>-2.9563</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9564</v>
+        <v>-2.8126</v>
       </c>
       <c r="G11" t="n">
         <v>-0.2019</v>
@@ -1312,13 +1312,13 @@
         <v>1.9576</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7843</v>
+        <v>-0.3485</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4264</v>
+        <v>-1.1344</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6421</v>
+        <v>0.7859</v>
       </c>
       <c r="V11" t="n">
         <v>-3.9135</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.5072</v>
+        <v>-7.0302</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0296</v>
+        <v>-4.7376</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4776</v>
+        <v>-2.2927</v>
       </c>
       <c r="G12" t="n">
         <v>-4.7573</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6422</v>
+        <v>-0.1652</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1524</v>
+        <v>-0.8604000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5102</v>
+        <v>0.6952</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8902</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.294</v>
+        <v>-6.5576</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.723</v>
+        <v>-14.038</v>
       </c>
       <c r="F13" t="n">
-        <v>7.429100000000001</v>
+        <v>7.480399999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.000199999999999</v>
+        <v>-4.0002</v>
       </c>
       <c r="H13" t="n">
         <v>2.904800000000001</v>
@@ -1468,13 +1468,13 @@
         <v>13.0503</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4901</v>
+        <v>2.2264</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.8041</v>
+        <v>-5.119200000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>7.294200000000001</v>
+        <v>7.345599999999999</v>
       </c>
       <c r="V13" t="n">
         <v>-2.609</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9575</v>
+        <v>4.2465</v>
       </c>
       <c r="E14" t="n">
-        <v>3.339</v>
+        <v>1.9979</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6185</v>
+        <v>2.2486</v>
       </c>
       <c r="G14" t="n">
         <v>2.3303</v>
@@ -1546,13 +1546,13 @@
         <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>2.867</v>
+        <v>1.156</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4132</v>
+        <v>0.0721</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4538</v>
+        <v>1.0839</v>
       </c>
       <c r="V14" t="n">
         <v>0.7602</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9427</v>
+        <v>3.9504</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6642</v>
+        <v>0.8878</v>
       </c>
       <c r="F15" t="n">
-        <v>3.2784</v>
+        <v>3.0626</v>
       </c>
       <c r="G15" t="n">
         <v>2.1139</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0429</v>
+        <v>-0.0352</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8904</v>
+        <v>-0.6669</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8475</v>
+        <v>0.6318</v>
       </c>
       <c r="V15" t="n">
         <v>0.3491</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6582</v>
+        <v>3.1117</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2345</v>
+        <v>0.5698</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4237</v>
+        <v>2.5419</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2357</v>
@@ -1702,13 +1702,13 @@
         <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1936</v>
+        <v>0.2599</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2329</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0393</v>
+        <v>1.1575</v>
       </c>
       <c r="V16" t="n">
         <v>1.13</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0978</v>
+        <v>3.0136</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3991</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6986</v>
+        <v>2.2792</v>
       </c>
       <c r="G17" t="n">
         <v>1.4907</v>
@@ -1780,13 +1780,13 @@
         <v>2.6101</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.5653</v>
+        <v>-0.6495</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.6439</v>
+        <v>-1.3086</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0786</v>
+        <v>0.6591</v>
       </c>
       <c r="V17" t="n">
         <v>2.8249</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DIAZ</t>
+          <t>J. YU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6223</v>
+        <v>1.6148</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5999</v>
+        <v>1.0413</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0224</v>
+        <v>0.5735</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9287</v>
+        <v>1.2162</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2867</v>
+        <v>1.621</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2153</v>
+        <v>-0.4048</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1329</v>
+        <v>2.3519</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2587</v>
+        <v>2.5033</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8742</v>
+        <v>-0.1514</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2042</v>
+        <v>-1.1357</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5453</v>
+        <v>-0.8823</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3411</v>
+        <v>-0.2534</v>
       </c>
       <c r="P18" t="n">
-        <v>-0</v>
+        <v>1.5225</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1751</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2586</v>
+        <v>0.006</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4879</v>
+        <v>-0.9409</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.9469</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>-0.3698</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.695</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. YU</t>
+          <t>G. MARTINEZ DIAZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2423</v>
+        <v>1.129</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8177</v>
+        <v>0.1529</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4245</v>
+        <v>0.9762</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2162</v>
+        <v>1.9287</v>
       </c>
       <c r="H19" t="n">
-        <v>1.621</v>
+        <v>-1.2867</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4048</v>
+        <v>3.2153</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3519</v>
+        <v>2.1329</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5033</v>
+        <v>0.2587</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1514</v>
+        <v>1.8742</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1357</v>
+        <v>-0.2042</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8823</v>
+        <v>-1.5453</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2534</v>
+        <v>1.3411</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5225</v>
+        <v>-0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5225</v>
+        <v>2.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3665</v>
+        <v>-0.2346</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1644</v>
+        <v>-0.9349</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7979000000000001</v>
+        <v>0.7003</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3698</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.7602</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3345</v>
+        <v>-0.2112</v>
       </c>
       <c r="E20" t="n">
         <v>-1.0493</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7148</v>
+        <v>0.8381</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2112</v>
@@ -2014,13 +2014,13 @@
         <v>0.435</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5583</v>
+        <v>-0.435</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3425</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2158</v>
+        <v>-0.0925</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0833</v>
+        <v>-0.4642</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4033</v>
+        <v>-1.1798</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3199</v>
+        <v>0.7155</v>
       </c>
       <c r="G21" t="n">
         <v>-1.1571</v>
@@ -2092,13 +2092,13 @@
         <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2536</v>
+        <v>-0.6345</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1644</v>
+        <v>-0.9409</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0892</v>
+        <v>0.3064</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7841</v>
+        <v>-2.0229</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5745</v>
+        <v>-3.3509</v>
       </c>
       <c r="F22" t="n">
-        <v>1.7904</v>
+        <v>1.328</v>
       </c>
       <c r="G22" t="n">
         <v>-2.3097</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3527</v>
+        <v>0.1139</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.5299</v>
       </c>
       <c r="U22" t="n">
-        <v>1.1061</v>
+        <v>0.6438</v>
       </c>
       <c r="V22" t="n">
         <v>0.3904</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.0248</v>
+        <v>-6.2773</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.4565</v>
+        <v>-7.233</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4317</v>
+        <v>0.9557</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1661</v>
@@ -2248,13 +2248,13 @@
         <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9882</v>
+        <v>-0.2406</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0274</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0393</v>
+        <v>0.5633</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9554</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.294100000000001</v>
+        <v>8.090399999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.429200000000002</v>
+        <v>-7.428900000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>14.7229</v>
+        <v>15.5193</v>
       </c>
       <c r="G24" t="n">
         <v>4</v>
@@ -2326,13 +2326,13 @@
         <v>15.2253</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4901</v>
+        <v>-0.6935999999999998</v>
       </c>
       <c r="T24" t="n">
-        <v>-7.2941</v>
+        <v>-7.294099999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>5.803999999999999</v>
+        <v>6.600499999999999</v>
       </c>
       <c r="V24" t="n">
         <v>2.609</v>
